--- a/artfynd/A 57053-2025 artfynd.xlsx
+++ b/artfynd/A 57053-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128305687</v>
+        <v>128305627</v>
       </c>
       <c r="B2" t="n">
-        <v>98632</v>
+        <v>96446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,33 +686,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -722,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>542725</v>
+        <v>542697</v>
       </c>
       <c r="R2" t="n">
-        <v>6390058</v>
+        <v>6390032</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128305703</v>
+        <v>128418269</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>96446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,33 +788,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1079</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -832,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>542736</v>
+        <v>542707</v>
       </c>
       <c r="R3" t="n">
-        <v>6390046</v>
+        <v>6390031</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,36 +879,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128305637</v>
+        <v>128305657</v>
       </c>
       <c r="B4" t="n">
-        <v>100820</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -934,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>542757</v>
+        <v>542722</v>
       </c>
       <c r="R4" t="n">
-        <v>6390057</v>
+        <v>6390068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +992,7 @@
         <v>128305672</v>
       </c>
       <c r="B5" t="n">
-        <v>98632</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128418269</v>
+        <v>128305687</v>
       </c>
       <c r="B6" t="n">
-        <v>95979</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,25 +1110,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1079</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>542707</v>
+        <v>542725</v>
       </c>
       <c r="R6" t="n">
-        <v>6390031</v>
+        <v>6390058</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,6 +1206,218 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128305703</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Försjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>542736</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6390046</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Pelarne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128305637</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Försjön, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>542757</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6390057</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Pelarne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulf Fransson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57053-2025 artfynd.xlsx
+++ b/artfynd/A 57053-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305627</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128418269</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305657</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305672</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305687</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1316,6 +1346,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305703</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,8 +1453,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128305637</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>